--- a/data/source/weekly/cs-en-us-094pct.xlsx
+++ b/data/source/weekly/cs-en-us-094pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -913,8 +913,8 @@
       <c r="H15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="15">
-        <v>1</v>
+      <c r="I15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>20</v>
@@ -923,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
         <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>-71.428571428571</v>
+        <v>-87.5</v>
       </c>
       <c r="I16" s="15">
         <v>6</v>
       </c>
       <c r="J16" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K16" s="14">
-        <v>-45.454545454545</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="L16" s="14">
-        <v>-53.846153846153</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M16" s="14">
         <v>-71.428571428571</v>
       </c>
       <c r="N16" s="14">
-        <v>-90.625</v>
+        <v>-91.780821917808</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,10 +981,10 @@
         <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
         <v>6</v>
@@ -996,22 +996,22 @@
         <v>-33.333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J17" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K17" s="14">
         <v>0</v>
       </c>
       <c r="L17" s="14">
-        <v>-8.333333333333</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M17" s="14">
-        <v>83.333333333333</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N17" s="14">
-        <v>-52.173913043478</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
         <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="15">
         <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>-78.571428571428</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I18" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J18" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K18" s="14">
-        <v>-72.222222222222</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="L18" s="14">
-        <v>-75</v>
+        <v>-65.217391304347</v>
       </c>
       <c r="M18" s="14">
-        <v>-77.272727272727</v>
+        <v>-68</v>
       </c>
       <c r="N18" s="14">
-        <v>-96.478873239436</v>
+        <v>-95.092024539877</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>-22.222222222222</v>
+        <v>30</v>
       </c>
       <c r="F19" s="15">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G19" s="15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H19" s="14">
-        <v>-16.216216216216</v>
+        <v>-7.894736842105</v>
       </c>
       <c r="I19" s="15">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="J19" s="15">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="K19" s="14">
-        <v>-26.315789473684</v>
+        <v>-17.910447761194</v>
       </c>
       <c r="L19" s="14">
-        <v>-37.313432835820</v>
+        <v>-27.631578947368</v>
       </c>
       <c r="M19" s="14">
-        <v>75</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N19" s="14">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1113,28 +1113,28 @@
         <v>7</v>
       </c>
       <c r="G20" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="I20" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J20" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K20" s="14">
-        <v>100</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L20" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="M20" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.636363636363</v>
+        <v>-89.215686274509</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
         <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-36.842105263157</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.985507246376</v>
+        <v>-26.027397260274</v>
       </c>
       <c r="I21" s="17">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="J21" s="17">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="K21" s="18">
-        <v>-26.470588235294</v>
+        <v>-23.140495867768</v>
       </c>
       <c r="L21" s="18">
-        <v>-36.440677966101</v>
+        <v>-30.597014925373</v>
       </c>
       <c r="M21" s="18">
-        <v>-7.407407407407</v>
+        <v>-4.123711340206</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.224376731301</v>
+        <v>-77.372262773722</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1204,10 +1204,10 @@
         <v>2</v>
       </c>
       <c r="J22" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="14">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L22" s="14">
         <v>-50</v>
@@ -1226,11 +1226,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="15">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1251,7 +1251,7 @@
         <v>-75</v>
       </c>
       <c r="L23" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E24" s="14">
-        <v>-30</v>
+        <v>100</v>
       </c>
       <c r="F24" s="15">
         <v>39</v>
       </c>
       <c r="G24" s="15">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H24" s="14">
-        <v>-38.095238095238</v>
+        <v>-22</v>
       </c>
       <c r="I24" s="15">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="J24" s="15">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K24" s="14">
-        <v>-26.190476190476</v>
+        <v>-15.217391304347</v>
       </c>
       <c r="L24" s="14">
-        <v>-37.373737373737</v>
+        <v>-32.758620689655</v>
       </c>
       <c r="M24" s="14">
-        <v>31.914893617021</v>
+        <v>52.941176470588</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>-80</v>
+        <v>50</v>
       </c>
       <c r="F25" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G25" s="15">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H25" s="14">
-        <v>-70.731707317073</v>
+        <v>-53.125</v>
       </c>
       <c r="I25" s="15">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J25" s="15">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K25" s="14">
-        <v>-61.666666666666</v>
+        <v>-54.6875</v>
       </c>
       <c r="L25" s="14">
-        <v>-51.063829787234</v>
+        <v>-50.847457627118</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G26" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H26" s="14">
-        <v>31.25</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I26" s="15">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J26" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K26" s="14">
-        <v>45.454545454545</v>
+        <v>34.615384615384</v>
       </c>
       <c r="L26" s="14">
-        <v>-3.030303030303</v>
+        <v>-14.634146341463</v>
       </c>
       <c r="M26" s="14">
-        <v>77.777777777777</v>
+        <v>52.173913043478</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,25 +1438,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="15">
         <v>5</v>
       </c>
       <c r="K28" s="14">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="L28" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,8 +1560,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-094pct.xlsx
+++ b/data/source/weekly/cs-en-us-094pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -913,8 +913,8 @@
       <c r="H15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>20</v>
+      <c r="I15" s="15">
+        <v>1</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>20</v>
@@ -923,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -940,7 +940,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
         <v>-100</v>
@@ -949,28 +949,28 @@
         <v>1</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>-87.5</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I16" s="15">
         <v>6</v>
       </c>
       <c r="J16" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="14">
-        <v>-53.846153846153</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L16" s="14">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="M16" s="14">
-        <v>-71.428571428571</v>
+        <v>-73.913043478260</v>
       </c>
       <c r="N16" s="14">
-        <v>-91.780821917808</v>
+        <v>-92.682926829268</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="F17" s="15">
         <v>6</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H17" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I17" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J17" s="15">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K17" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L17" s="14">
-        <v>-13.333333333333</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M17" s="14">
-        <v>85.714285714285</v>
+        <v>100</v>
       </c>
       <c r="N17" s="14">
-        <v>-50</v>
+        <v>-40.740740740740</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G18" s="15">
+        <v>12</v>
+      </c>
+      <c r="H18" s="14">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="I18" s="15">
         <v>14</v>
       </c>
-      <c r="H18" s="14">
-        <v>-64.285714285714</v>
-      </c>
-      <c r="I18" s="15">
-        <v>8</v>
-      </c>
       <c r="J18" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K18" s="14">
-        <v>-61.904761904761</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="L18" s="14">
-        <v>-65.217391304347</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="M18" s="14">
-        <v>-68</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.092024539877</v>
+        <v>-92.746113989637</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>30</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F19" s="15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G19" s="15">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H19" s="14">
-        <v>-7.894736842105</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="I19" s="15">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J19" s="15">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="K19" s="14">
-        <v>-17.910447761194</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L19" s="14">
-        <v>-27.631578947368</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="M19" s="14">
-        <v>66.666666666666</v>
+        <v>68.421052631578</v>
       </c>
       <c r="N19" s="14">
-        <v>22.222222222222</v>
+        <v>30.612244897959</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F20" s="15">
+        <v>10</v>
+      </c>
+      <c r="G20" s="15">
         <v>7</v>
       </c>
-      <c r="G20" s="15">
-        <v>4</v>
-      </c>
       <c r="H20" s="14">
-        <v>75</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I20" s="15">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J20" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K20" s="14">
-        <v>57.142857142857</v>
+        <v>60</v>
       </c>
       <c r="L20" s="14">
-        <v>120</v>
+        <v>128.571428571429</v>
       </c>
       <c r="M20" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.215686274509</v>
+        <v>-86.206896551724</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1145,75 +1145,75 @@
         <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="F21" s="17">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G21" s="17">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.027397260274</v>
+        <v>-14.864864864864</v>
       </c>
       <c r="I21" s="17">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="J21" s="17">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.140495867768</v>
+        <v>-17.021276595744</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.597014925373</v>
+        <v>-23.026315789473</v>
       </c>
       <c r="M21" s="18">
-        <v>-4.123711340206</v>
+        <v>3.539823008849</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.372262773722</v>
+        <v>-75.053304904051</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="15">
         <v>1</v>
       </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="15">
         <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="15">
         <v>7</v>
       </c>
       <c r="K22" s="14">
-        <v>-71.428571428571</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L22" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M22" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,35 +1223,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15">
+        <v>1</v>
       </c>
       <c r="G23" s="15">
         <v>3</v>
       </c>
       <c r="H23" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" s="14">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="L23" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D24" s="15">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E24" s="14">
-        <v>100</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="F24" s="15">
         <v>39</v>
       </c>
       <c r="G24" s="15">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="H24" s="14">
-        <v>-22</v>
+        <v>-33.898305084745</v>
       </c>
       <c r="I24" s="15">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J24" s="15">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="K24" s="14">
-        <v>-15.217391304347</v>
+        <v>-23.423423423423</v>
       </c>
       <c r="L24" s="14">
-        <v>-32.758620689655</v>
+        <v>-38.405797101449</v>
       </c>
       <c r="M24" s="14">
-        <v>52.941176470588</v>
+        <v>34.920634920634</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E25" s="14">
-        <v>50</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="F25" s="15">
         <v>15</v>
       </c>
       <c r="G25" s="15">
+        <v>37</v>
+      </c>
+      <c r="H25" s="14">
+        <v>-59.459459459459</v>
+      </c>
+      <c r="I25" s="15">
         <v>32</v>
       </c>
-      <c r="H25" s="14">
-        <v>-53.125</v>
-      </c>
-      <c r="I25" s="15">
-        <v>29</v>
-      </c>
       <c r="J25" s="15">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="K25" s="14">
-        <v>-54.6875</v>
+        <v>-58.974358974359</v>
       </c>
       <c r="L25" s="14">
-        <v>-50.847457627118</v>
+        <v>-54.929577464788</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>8</v>
+      </c>
+      <c r="D26" s="15">
         <v>3</v>
       </c>
-      <c r="D26" s="15">
-        <v>4</v>
-      </c>
       <c r="E26" s="14">
-        <v>-25</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F26" s="15">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G26" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H26" s="14">
-        <v>5.882352941176</v>
+        <v>50</v>
       </c>
       <c r="I26" s="15">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J26" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K26" s="14">
-        <v>34.615384615384</v>
+        <v>44.827586206896</v>
       </c>
       <c r="L26" s="14">
-        <v>-14.634146341463</v>
+        <v>0</v>
       </c>
       <c r="M26" s="14">
-        <v>52.173913043478</v>
+        <v>68</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="15">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
         <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K28" s="14">
-        <v>-40</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L28" s="14">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1637,8 +1637,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="14">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-094pct.xlsx
+++ b/data/source/weekly/cs-en-us-094pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -904,8 +904,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="15">
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,7 +914,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>20</v>
@@ -923,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="15">
         <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J16" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="14">
-        <v>-57.142857142857</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>-62.5</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="M16" s="14">
-        <v>-73.913043478260</v>
+        <v>-70.833333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.682926829268</v>
+        <v>-92.391304347826</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,37 +981,37 @@
         <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
         <v>6</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" s="14">
-        <v>-50</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I17" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J17" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K17" s="14">
-        <v>-11.111111111111</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="L17" s="14">
-        <v>-5.882352941176</v>
+        <v>-15</v>
       </c>
       <c r="M17" s="14">
-        <v>100</v>
+        <v>88.888888888888</v>
       </c>
       <c r="N17" s="14">
-        <v>-40.740740740740</v>
+        <v>-39.285714285714</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
+        <v>14</v>
+      </c>
+      <c r="G18" s="15">
         <v>10</v>
       </c>
-      <c r="G18" s="15">
-        <v>12</v>
-      </c>
       <c r="H18" s="14">
-        <v>-16.666666666666</v>
+        <v>40</v>
       </c>
       <c r="I18" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J18" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K18" s="14">
-        <v>-39.130434782608</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>-48.148148148148</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M18" s="14">
-        <v>-46.153846153846</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.746113989637</v>
+        <v>-91.469194312796</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E19" s="14">
-        <v>-11.111111111111</v>
+        <v>-60</v>
       </c>
       <c r="F19" s="15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G19" s="15">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H19" s="14">
-        <v>-2.702702702702</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="I19" s="15">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="J19" s="15">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="K19" s="14">
-        <v>-15.789473684210</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L19" s="14">
-        <v>-23.809523809523</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M19" s="14">
-        <v>68.421052631578</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N19" s="14">
-        <v>30.612244897959</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
         <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="15">
+        <v>8</v>
+      </c>
+      <c r="G20" s="15">
         <v>10</v>
       </c>
-      <c r="G20" s="15">
-        <v>7</v>
-      </c>
       <c r="H20" s="14">
-        <v>42.857142857142</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K20" s="14">
-        <v>60</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L20" s="14">
-        <v>128.571428571429</v>
+        <v>70</v>
       </c>
       <c r="M20" s="14">
-        <v>-11.111111111111</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="N20" s="14">
-        <v>-86.206896551724</v>
+        <v>-88.111888111888</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,78 +1142,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-5</v>
+        <v>-37.5</v>
       </c>
       <c r="F21" s="17">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G21" s="17">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.864864864864</v>
+        <v>-20.731707317073</v>
       </c>
       <c r="I21" s="17">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="J21" s="17">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.021276595744</v>
+        <v>-20.606060606060</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.026315789473</v>
+        <v>-22.023809523809</v>
       </c>
       <c r="M21" s="18">
-        <v>3.539823008849</v>
+        <v>2.34375</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.053304904051</v>
+        <v>-75.375939849624</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="15">
+        <v>2</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="15">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
-        <v>2</v>
-      </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="15">
         <v>3</v>
       </c>
       <c r="J22" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K22" s="14">
-        <v>-57.142857142857</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L22" s="14">
         <v>-25</v>
       </c>
       <c r="M22" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1226,35 +1226,35 @@
       <c r="C23" s="15">
         <v>1</v>
       </c>
-      <c r="D23" s="15">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="15">
+        <v>2</v>
+      </c>
+      <c r="G23" s="15">
+        <v>2</v>
+      </c>
+      <c r="H23" s="14">
         <v>0</v>
       </c>
-      <c r="F23" s="15">
-        <v>1</v>
-      </c>
-      <c r="G23" s="15">
+      <c r="I23" s="15">
         <v>3</v>
-      </c>
-      <c r="H23" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="I23" s="15">
-        <v>2</v>
       </c>
       <c r="J23" s="15">
         <v>5</v>
       </c>
       <c r="K23" s="14">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="L23" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="M23" s="13" t="s">
-        <v>21</v>
+        <v>-50</v>
+      </c>
+      <c r="M23" s="14">
+        <v>200</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D24" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>-63.157894736842</v>
+        <v>-87.5</v>
       </c>
       <c r="F24" s="15">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G24" s="15">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H24" s="14">
-        <v>-33.898305084745</v>
+        <v>-45.901639344262</v>
       </c>
       <c r="I24" s="15">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J24" s="15">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.423423423423</v>
+        <v>-34.814814814814</v>
       </c>
       <c r="L24" s="14">
-        <v>-38.405797101449</v>
+        <v>-48.235294117647</v>
       </c>
       <c r="M24" s="14">
-        <v>34.920634920634</v>
+        <v>23.943661971831</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E25" s="14">
-        <v>-78.571428571428</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G25" s="15">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H25" s="14">
-        <v>-59.459459459459</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I25" s="15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J25" s="15">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K25" s="14">
-        <v>-58.974358974359</v>
+        <v>-61.363636363636</v>
       </c>
       <c r="L25" s="14">
-        <v>-54.929577464788</v>
+        <v>-60.465116279069</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>166.666666666667</v>
+        <v>20</v>
       </c>
       <c r="F26" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G26" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H26" s="14">
-        <v>50</v>
+        <v>38.888888888888</v>
       </c>
       <c r="I26" s="15">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J26" s="15">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K26" s="14">
-        <v>44.827586206896</v>
+        <v>41.176470588235</v>
       </c>
       <c r="L26" s="14">
-        <v>0</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M26" s="14">
-        <v>68</v>
+        <v>41.176470588235</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1396,8 +1396,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="15">
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1406,7 +1406,7 @@
         <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>20</v>
@@ -1415,7 +1415,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,23 +1428,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I28" s="15">
         <v>5</v>
@@ -1456,7 +1456,7 @@
         <v>-28.571428571428</v>
       </c>
       <c r="L28" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1613,29 +1613,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="15">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="14">
+        <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="15">
+        <v>1</v>
+      </c>
+      <c r="K33" s="14">
+        <v>-100</v>
       </c>
       <c r="L33" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-094pct.xlsx
+++ b/data/source/weekly/cs-en-us-094pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -923,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
-      </c>
-      <c r="F16" s="15">
-        <v>2</v>
+        <v>-100</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G16" s="15">
         <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I16" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J16" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K16" s="14">
-        <v>-53.333333333333</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="L16" s="14">
-        <v>-61.111111111111</v>
+        <v>-70</v>
       </c>
       <c r="M16" s="14">
-        <v>-70.833333333333</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.391304347826</v>
+        <v>-94.285714285714</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
         <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>-53.846153846153</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I17" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J17" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K17" s="14">
-        <v>-10.526315789473</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L17" s="14">
-        <v>-15</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="M17" s="14">
-        <v>88.888888888888</v>
+        <v>100</v>
       </c>
       <c r="N17" s="14">
-        <v>-39.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>4</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G18" s="15">
         <v>10</v>
       </c>
       <c r="H18" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I18" s="15">
         <v>18</v>
       </c>
       <c r="J18" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K18" s="14">
-        <v>-33.333333333333</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L18" s="14">
-        <v>-35.714285714285</v>
+        <v>-40</v>
       </c>
       <c r="M18" s="14">
-        <v>-47.058823529411</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="N18" s="14">
-        <v>-91.469194312796</v>
+        <v>-92.241379310344</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>-60</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F19" s="15">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G19" s="15">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H19" s="14">
-        <v>-20.930232558139</v>
+        <v>-17.777777777777</v>
       </c>
       <c r="I19" s="15">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J19" s="15">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="K19" s="14">
-        <v>-23.076923076923</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="L19" s="14">
-        <v>-23.076923076923</v>
+        <v>-27.678571428571</v>
       </c>
       <c r="M19" s="14">
-        <v>66.666666666666</v>
+        <v>58.823529411764</v>
       </c>
       <c r="N19" s="14">
-        <v>25</v>
+        <v>28.571428571428</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
-      </c>
-      <c r="D20" s="15">
-        <v>3</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-33.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
         <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" s="15">
         <v>13</v>
       </c>
       <c r="K20" s="14">
-        <v>30.769230769230</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L20" s="14">
-        <v>70</v>
+        <v>63.636363636363</v>
       </c>
       <c r="M20" s="14">
-        <v>-10.526315789473</v>
+        <v>-10</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.111888111888</v>
+        <v>-88.679245283018</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>-37.5</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F21" s="17">
         <v>65</v>
       </c>
       <c r="G21" s="17">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.731707317073</v>
+        <v>-18.75</v>
       </c>
       <c r="I21" s="17">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="J21" s="17">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.606060606060</v>
+        <v>-20.329670329670</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.023809523809</v>
+        <v>-26.767676767676</v>
       </c>
       <c r="M21" s="18">
-        <v>2.34375</v>
+        <v>-0.684931506849</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.375939849624</v>
+        <v>-75.465313028764</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,20 +1185,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>2</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
       </c>
       <c r="G22" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="15">
         <v>3</v>
@@ -1210,7 +1210,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L22" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="M22" s="14">
         <v>0</v>
@@ -1223,8 +1223,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1236,10 +1236,10 @@
         <v>2</v>
       </c>
       <c r="G23" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23" s="15">
         <v>3</v>
@@ -1254,7 +1254,7 @@
         <v>-50</v>
       </c>
       <c r="M23" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D24" s="15">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E24" s="14">
-        <v>-87.5</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="F24" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G24" s="15">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="H24" s="14">
-        <v>-45.901639344262</v>
+        <v>-47.142857142857</v>
       </c>
       <c r="I24" s="15">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="J24" s="15">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="K24" s="14">
-        <v>-34.814814814814</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L24" s="14">
-        <v>-48.235294117647</v>
+        <v>-46.486486486486</v>
       </c>
       <c r="M24" s="14">
-        <v>23.943661971831</v>
+        <v>23.75</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E25" s="14">
-        <v>-80</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G25" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H25" s="14">
-        <v>-63.636363636363</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I25" s="15">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J25" s="15">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="K25" s="14">
-        <v>-61.363636363636</v>
+        <v>-60.416666666666</v>
       </c>
       <c r="L25" s="14">
-        <v>-60.465116279069</v>
+        <v>-63.461538461538</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
         <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F26" s="15">
         <v>25</v>
       </c>
       <c r="G26" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H26" s="14">
-        <v>38.888888888888</v>
+        <v>47.058823529411</v>
       </c>
       <c r="I26" s="15">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="J26" s="15">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K26" s="14">
-        <v>41.176470588235</v>
+        <v>43.589743589743</v>
       </c>
       <c r="L26" s="14">
-        <v>6.666666666666</v>
+        <v>21.739130434782</v>
       </c>
       <c r="M26" s="14">
-        <v>41.176470588235</v>
+        <v>47.368421052631</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1415,7 +1415,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1431,29 +1431,29 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
         <v>5</v>
       </c>
       <c r="J28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="L28" s="14">
         <v>0</v>
@@ -1554,29 +1554,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>1</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="15">
+        <v>1</v>
+      </c>
+      <c r="K31" s="14">
+        <v>0</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>
@@ -1613,11 +1613,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="15">
-        <v>1</v>
-      </c>
-      <c r="E33" s="14">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-094pct.xlsx
+++ b/data/source/weekly/cs-en-us-094pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,7 +914,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>20</v>
@@ -923,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -940,7 +940,7 @@
         <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
         <v>-100</v>
@@ -949,7 +949,7 @@
         <v>20</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
         <v>-100</v>
@@ -958,10 +958,10 @@
         <v>6</v>
       </c>
       <c r="J16" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K16" s="14">
-        <v>-64.705882352941</v>
+        <v>-70</v>
       </c>
       <c r="L16" s="14">
         <v>-70</v>
@@ -970,7 +970,7 @@
         <v>-76.923076923076</v>
       </c>
       <c r="N16" s="14">
-        <v>-94.285714285714</v>
+        <v>-94.915254237288</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F17" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G17" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H17" s="14">
-        <v>-36.363636363636</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I17" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K17" s="14">
-        <v>-9.090909090909</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="L17" s="14">
-        <v>-13.043478260869</v>
+        <v>-16</v>
       </c>
       <c r="M17" s="14">
-        <v>100</v>
+        <v>61.538461538461</v>
       </c>
       <c r="N17" s="14">
-        <v>-33.333333333333</v>
+        <v>-34.375</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>20</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I18" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K18" s="14">
-        <v>-35.714285714285</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>-40</v>
+        <v>-40.625</v>
       </c>
       <c r="M18" s="14">
-        <v>-53.846153846153</v>
+        <v>-54.761904761904</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.241379310344</v>
+        <v>-92.490118577075</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>11</v>
+      </c>
+      <c r="D19" s="15">
         <v>10</v>
       </c>
-      <c r="D19" s="15">
-        <v>11</v>
-      </c>
       <c r="E19" s="14">
-        <v>-9.090909090909</v>
+        <v>10</v>
       </c>
       <c r="F19" s="15">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G19" s="15">
         <v>45</v>
       </c>
       <c r="H19" s="14">
-        <v>-17.777777777777</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I19" s="15">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J19" s="15">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="K19" s="14">
-        <v>-20.588235294117</v>
+        <v>-16.964285714285</v>
       </c>
       <c r="L19" s="14">
-        <v>-27.678571428571</v>
+        <v>-21.186440677966</v>
       </c>
       <c r="M19" s="14">
-        <v>58.823529411764</v>
+        <v>66.071428571428</v>
       </c>
       <c r="N19" s="14">
-        <v>28.571428571428</v>
+        <v>40.909090909090</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D20" s="15">
+        <v>2</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G20" s="15">
         <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I20" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J20" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K20" s="14">
-        <v>38.461538461538</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>63.636363636363</v>
+        <v>53.846153846153</v>
       </c>
       <c r="M20" s="14">
-        <v>-10</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.679245283018</v>
+        <v>-88.095238095238</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.647058823529</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="F21" s="17">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G21" s="17">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.75</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="I21" s="17">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="J21" s="17">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.329670329670</v>
+        <v>-20.197044334975</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.767676767676</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.684931506849</v>
+        <v>2.531645569620</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.465313028764</v>
+        <v>-74.647887323943</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1195,10 +1195,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="15">
         <v>3</v>
@@ -1254,7 +1254,7 @@
         <v>-50</v>
       </c>
       <c r="M23" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D24" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E24" s="14">
-        <v>-42.105263157894</v>
+        <v>6.25</v>
       </c>
       <c r="F24" s="15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G24" s="15">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H24" s="14">
-        <v>-47.142857142857</v>
+        <v>-51.282051282051</v>
       </c>
       <c r="I24" s="15">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="J24" s="15">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="K24" s="14">
-        <v>-35.714285714285</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="L24" s="14">
-        <v>-46.486486486486</v>
+        <v>-44.174757281553</v>
       </c>
       <c r="M24" s="14">
-        <v>23.75</v>
+        <v>21.052631578947</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F25" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G25" s="15">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H25" s="14">
-        <v>-58.333333333333</v>
+        <v>-67.441860465116</v>
       </c>
       <c r="I25" s="15">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J25" s="15">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="K25" s="14">
-        <v>-60.416666666666</v>
+        <v>-59.813084112149</v>
       </c>
       <c r="L25" s="14">
-        <v>-63.461538461538</v>
+        <v>-64.166666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" s="14">
-        <v>60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G26" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H26" s="14">
-        <v>47.058823529411</v>
+        <v>50</v>
       </c>
       <c r="I26" s="15">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J26" s="15">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K26" s="14">
-        <v>43.589743589743</v>
+        <v>38.095238095238</v>
       </c>
       <c r="L26" s="14">
-        <v>21.739130434782</v>
+        <v>16</v>
       </c>
       <c r="M26" s="14">
-        <v>47.368421052631</v>
+        <v>45</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
+        <v>2</v>
+      </c>
+      <c r="G27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="H27" s="14">
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="J27" s="15">
+        <v>1</v>
+      </c>
+      <c r="K27" s="14">
+        <v>200</v>
       </c>
       <c r="L27" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J28" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28" s="14">
-        <v>-37.5</v>
+        <v>-30</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1499,8 +1499,8 @@
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+      <c r="M29" s="14">
+        <v>-100</v>
       </c>
       <c r="N29" s="14">
         <v>-100</v>
@@ -1540,8 +1540,8 @@
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+      <c r="M30" s="14">
+        <v>-100</v>
       </c>
       <c r="N30" s="14">
         <v>-100</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-094pct.xlsx
+++ b/data/source/weekly/cs-en-us-094pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -923,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -936,82 +936,82 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>3</v>
       </c>
       <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>200</v>
+      </c>
+      <c r="F16" s="15">
         <v>3</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="G16" s="15">
         <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>-100</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I16" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J16" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" s="14">
-        <v>-70</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L16" s="14">
-        <v>-70</v>
+        <v>-60.869565217391</v>
       </c>
       <c r="M16" s="14">
-        <v>-76.923076923076</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N16" s="14">
-        <v>-94.915254237288</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>1</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17" s="15">
         <v>13</v>
       </c>
       <c r="H17" s="14">
-        <v>-53.846153846153</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="I17" s="15">
         <v>21</v>
       </c>
       <c r="J17" s="15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K17" s="14">
-        <v>-19.230769230769</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="L17" s="14">
-        <v>-16</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M17" s="14">
         <v>61.538461538461</v>
       </c>
       <c r="N17" s="14">
-        <v>-34.375</v>
+        <v>-46.153846153846</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,37 +1022,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
+        <v>6</v>
+      </c>
+      <c r="G18" s="15">
         <v>10</v>
       </c>
-      <c r="G18" s="15">
-        <v>9</v>
-      </c>
       <c r="H18" s="14">
-        <v>11.111111111111</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K18" s="14">
-        <v>-36.666666666666</v>
+        <v>-39.393939393939</v>
       </c>
       <c r="L18" s="14">
-        <v>-40.625</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M18" s="14">
-        <v>-54.761904761904</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.490118577075</v>
+        <v>-92.424242424242</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
         <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>10</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G19" s="15">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H19" s="14">
-        <v>-22.222222222222</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="I19" s="15">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J19" s="15">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="K19" s="14">
-        <v>-16.964285714285</v>
+        <v>-18.032786885245</v>
       </c>
       <c r="L19" s="14">
-        <v>-21.186440677966</v>
+        <v>-24.812030075188</v>
       </c>
       <c r="M19" s="14">
-        <v>66.071428571428</v>
+        <v>61.290322580645</v>
       </c>
       <c r="N19" s="14">
-        <v>40.909090909090</v>
+        <v>29.870129870129</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
         <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
         <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J20" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K20" s="14">
-        <v>33.333333333333</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L20" s="14">
-        <v>53.846153846153</v>
+        <v>76.923076923076</v>
       </c>
       <c r="M20" s="14">
-        <v>-4.761904761904</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.095238095238</v>
+        <v>-87.958115183246</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,78 +1142,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-23.809523809523</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="F21" s="17">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G21" s="17">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H21" s="18">
-        <v>-24.390243902439</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I21" s="17">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="J21" s="17">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.197044334975</v>
+        <v>-21.777777777777</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.857142857142</v>
+        <v>-24.786324786324</v>
       </c>
       <c r="M21" s="18">
-        <v>2.531645569620</v>
+        <v>4.142011834319</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.647887323943</v>
+        <v>-75.141242937853</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K22" s="14">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="L22" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1233,13 +1233,13 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>2</v>
-      </c>
-      <c r="G23" s="15">
         <v>1</v>
       </c>
-      <c r="H23" s="14">
-        <v>100</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="15">
         <v>3</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D24" s="15">
         <v>16</v>
       </c>
       <c r="E24" s="14">
-        <v>6.25</v>
+        <v>-25</v>
       </c>
       <c r="F24" s="15">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G24" s="15">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H24" s="14">
-        <v>-51.282051282051</v>
+        <v>-42.666666666666</v>
       </c>
       <c r="I24" s="15">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="J24" s="15">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="K24" s="14">
-        <v>-32.352941176470</v>
+        <v>-31.720430107526</v>
       </c>
       <c r="L24" s="14">
-        <v>-44.174757281553</v>
+        <v>-45.258620689655</v>
       </c>
       <c r="M24" s="14">
-        <v>21.052631578947</v>
+        <v>20.952380952381</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E25" s="14">
-        <v>-54.545454545454</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F25" s="15">
         <v>14</v>
       </c>
       <c r="G25" s="15">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H25" s="14">
-        <v>-67.441860465116</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="I25" s="15">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J25" s="15">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K25" s="14">
-        <v>-59.813084112149</v>
+        <v>-59.649122807017</v>
       </c>
       <c r="L25" s="14">
-        <v>-64.166666666666</v>
+        <v>-65.925925925925</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>2</v>
       </c>
       <c r="D26" s="15">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>-33.333333333333</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F26" s="15">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G26" s="15">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H26" s="14">
-        <v>50</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I26" s="15">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J26" s="15">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K26" s="14">
-        <v>38.095238095238</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L26" s="14">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M26" s="14">
-        <v>45</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="15">
         <v>1</v>
       </c>
       <c r="K27" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L27" s="14">
         <v>0</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
+        <v>1</v>
+      </c>
+      <c r="G28" s="15">
         <v>4</v>
       </c>
-      <c r="G28" s="15">
-        <v>5</v>
-      </c>
       <c r="H28" s="14">
-        <v>-20</v>
+        <v>-75</v>
       </c>
       <c r="I28" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J28" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="14">
-        <v>-30</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L28" s="14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1613,17 +1613,17 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="15">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G33" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="14">
         <v>-100</v>
@@ -1632,7 +1632,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-094pct.xlsx
+++ b/data/source/weekly/cs-en-us-094pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -925,8 +925,8 @@
       <c r="L15" s="14">
         <v>0</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+      <c r="M15" s="14">
+        <v>200</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>21</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
-      </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>-57.142857142857</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16" s="15">
         <v>21</v>
       </c>
       <c r="K16" s="14">
-        <v>-57.142857142857</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="L16" s="14">
-        <v>-60.869565217391</v>
+        <v>-60</v>
       </c>
       <c r="M16" s="14">
-        <v>-66.666666666666</v>
+        <v>-62.962962962963</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.333333333333</v>
+        <v>-93.150684931506</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,78 +981,78 @@
         <v>20</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
         <v>-100</v>
       </c>
       <c r="F17" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="14">
-        <v>-61.538461538461</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I17" s="15">
         <v>21</v>
       </c>
       <c r="J17" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K17" s="14">
-        <v>-32.258064516129</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L17" s="14">
-        <v>-22.222222222222</v>
+        <v>-25</v>
       </c>
       <c r="M17" s="14">
         <v>61.538461538461</v>
       </c>
       <c r="N17" s="14">
-        <v>-46.153846153846</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
         <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>-40</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I18" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J18" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K18" s="14">
-        <v>-39.393939393939</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="L18" s="14">
-        <v>-42.857142857142</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M18" s="14">
-        <v>-54.545454545454</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.424242424242</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,60 +1060,60 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>6</v>
+      </c>
+      <c r="D19" s="15">
         <v>8</v>
       </c>
-      <c r="D19" s="15">
-        <v>10</v>
-      </c>
       <c r="E19" s="14">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="15">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G19" s="15">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H19" s="14">
-        <v>-21.739130434782</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="I19" s="15">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="J19" s="15">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="K19" s="14">
-        <v>-18.032786885245</v>
+        <v>-17.692307692307</v>
       </c>
       <c r="L19" s="14">
-        <v>-24.812030075188</v>
+        <v>-26.712328767123</v>
       </c>
       <c r="M19" s="14">
-        <v>61.290322580645</v>
+        <v>46.575342465753</v>
       </c>
       <c r="N19" s="14">
-        <v>29.870129870129</v>
+        <v>24.418604651162</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>3</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
         <v>0</v>
@@ -1122,19 +1122,19 @@
         <v>23</v>
       </c>
       <c r="J20" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" s="14">
-        <v>27.777777777777</v>
+        <v>21.052631578947</v>
       </c>
       <c r="L20" s="14">
-        <v>76.923076923076</v>
+        <v>53.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>0</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="N20" s="14">
-        <v>-87.958115183246</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,63 +1142,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-31.818181818181</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G21" s="17">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.571428571428</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="I21" s="17">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="J21" s="17">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.777777777777</v>
+        <v>-22.175732217573</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.786324786324</v>
+        <v>-26.482213438735</v>
       </c>
       <c r="M21" s="18">
-        <v>4.142011834319</v>
+        <v>-0.534759358288</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.141242937853</v>
+        <v>-76.030927835051</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>0</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
         <v>4</v>
@@ -1213,7 +1213,7 @@
         <v>-20</v>
       </c>
       <c r="M22" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1232,8 +1232,8 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="15">
-        <v>1</v>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
@@ -1268,34 +1268,34 @@
         <v>12</v>
       </c>
       <c r="D24" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E24" s="14">
-        <v>-25</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F24" s="15">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G24" s="15">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H24" s="14">
-        <v>-42.666666666666</v>
+        <v>-27.142857142857</v>
       </c>
       <c r="I24" s="15">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="J24" s="15">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="K24" s="14">
-        <v>-31.720430107526</v>
+        <v>-32.682926829268</v>
       </c>
       <c r="L24" s="14">
-        <v>-45.258620689655</v>
+        <v>-44.578313253012</v>
       </c>
       <c r="M24" s="14">
-        <v>20.952380952381</v>
+        <v>25.454545454545</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25" s="14">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G25" s="15">
         <v>36</v>
       </c>
       <c r="H25" s="14">
-        <v>-61.111111111111</v>
+        <v>-52.777777777777</v>
       </c>
       <c r="I25" s="15">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J25" s="15">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K25" s="14">
-        <v>-59.649122807017</v>
+        <v>-58.870967741935</v>
       </c>
       <c r="L25" s="14">
-        <v>-65.925925925925</v>
+        <v>-64.827586206896</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>-77.777777777777</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G26" s="15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H26" s="14">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J26" s="15">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K26" s="14">
-        <v>17.647058823529</v>
+        <v>25.454545454545</v>
       </c>
       <c r="L26" s="14">
-        <v>0</v>
+        <v>11.290322580645</v>
       </c>
       <c r="M26" s="14">
-        <v>42.857142857142</v>
+        <v>60.465116279069</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,25 +1397,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="15">
         <v>1</v>
       </c>
       <c r="K27" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1431,11 +1431,11 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>1</v>
@@ -1447,16 +1447,16 @@
         <v>-75</v>
       </c>
       <c r="I28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J28" s="15">
         <v>11</v>
       </c>
       <c r="K28" s="14">
-        <v>-45.454545454545</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L28" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1613,17 +1613,17 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="15">
         <v>1</v>
-      </c>
-      <c r="E33" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="15">
-        <v>2</v>
       </c>
       <c r="H33" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-094pct.xlsx
+++ b/data/source/weekly/cs-en-us-094pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,7 +914,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>20</v>
@@ -923,10 +923,10 @@
         <v>21</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>21</v>
@@ -939,52 +939,52 @@
       <c r="C16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="15">
+        <v>4</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J16" s="15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K16" s="14">
-        <v>-52.380952380952</v>
+        <v>-52</v>
       </c>
       <c r="L16" s="14">
-        <v>-60</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="M16" s="14">
-        <v>-62.962962962963</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.150684931506</v>
+        <v>-92.638036809816</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="15">
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
         <v>4</v>
@@ -996,22 +996,22 @@
         <v>-71.428571428571</v>
       </c>
       <c r="I17" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J17" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K17" s="14">
-        <v>-36.363636363636</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>-25</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="M17" s="14">
-        <v>61.538461538461</v>
+        <v>71.428571428571</v>
       </c>
       <c r="N17" s="14">
-        <v>-57.142857142857</v>
+        <v>-54.716981132075</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,7 +1022,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
         <v>-100</v>
@@ -1031,28 +1031,28 @@
         <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>-55.555555555555</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="I18" s="15">
         <v>22</v>
       </c>
       <c r="J18" s="15">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K18" s="14">
-        <v>-38.888888888888</v>
+        <v>-46.341463414634</v>
       </c>
       <c r="L18" s="14">
-        <v>-38.888888888888</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="M18" s="14">
-        <v>-52.173913043478</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.307692307692</v>
+        <v>-92.971246006389</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E19" s="14">
-        <v>-25</v>
+        <v>120</v>
       </c>
       <c r="F19" s="15">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G19" s="15">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H19" s="14">
-        <v>-10.256410256410</v>
+        <v>12.121212121212</v>
       </c>
       <c r="I19" s="15">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="J19" s="15">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K19" s="14">
-        <v>-17.692307692307</v>
+        <v>-11.851851851851</v>
       </c>
       <c r="L19" s="14">
-        <v>-26.712328767123</v>
+        <v>-25.157232704402</v>
       </c>
       <c r="M19" s="14">
-        <v>46.575342465753</v>
+        <v>50.632911392405</v>
       </c>
       <c r="N19" s="14">
-        <v>24.418604651162</v>
+        <v>27.956989247311</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1104,37 +1104,37 @@
         <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
         <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-37.5</v>
       </c>
       <c r="I20" s="15">
         <v>23</v>
       </c>
       <c r="J20" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K20" s="14">
-        <v>21.052631578947</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L20" s="14">
         <v>53.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>-14.814814814814</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.888888888888</v>
+        <v>-89.545454545454</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-42.857142857142</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="F21" s="17">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G21" s="17">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H21" s="18">
-        <v>-27.027027027027</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="I21" s="17">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="J21" s="17">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="K21" s="18">
-        <v>-22.175732217573</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.482213438735</v>
+        <v>-25</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.534759358288</v>
+        <v>3.553299492385</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.030927835051</v>
+        <v>-75.829383886255</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1213,7 +1213,7 @@
         <v>-20</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1226,32 +1226,32 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>-100</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14">
+        <v>-100</v>
       </c>
       <c r="I23" s="15">
         <v>3</v>
       </c>
       <c r="J23" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K23" s="14">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="14">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="M23" s="14">
         <v>-50</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D24" s="15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" s="14">
-        <v>-36.842105263157</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F24" s="15">
         <v>51</v>
       </c>
       <c r="G24" s="15">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H24" s="14">
-        <v>-27.142857142857</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="I24" s="15">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="J24" s="15">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="K24" s="14">
-        <v>-32.682926829268</v>
+        <v>-33.183856502242</v>
       </c>
       <c r="L24" s="14">
-        <v>-44.578313253012</v>
+        <v>-42.023346303501</v>
       </c>
       <c r="M24" s="14">
-        <v>25.454545454545</v>
+        <v>25.210084033613</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E25" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F25" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G25" s="15">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H25" s="14">
-        <v>-52.777777777777</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I25" s="15">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J25" s="15">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="K25" s="14">
-        <v>-58.870967741935</v>
+        <v>-55.725190839694</v>
       </c>
       <c r="L25" s="14">
-        <v>-64.827586206896</v>
+        <v>-60.810810810810</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,10 +1350,10 @@
         <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F26" s="15">
         <v>21</v>
@@ -1365,19 +1365,19 @@
         <v>0</v>
       </c>
       <c r="I26" s="15">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J26" s="15">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K26" s="14">
-        <v>25.454545454545</v>
+        <v>28.333333333333</v>
       </c>
       <c r="L26" s="14">
-        <v>11.290322580645</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M26" s="14">
-        <v>60.465116279069</v>
+        <v>79.069767441860</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,25 +1397,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="15">
         <v>1</v>
       </c>
       <c r="K27" s="14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L27" s="14">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1441,10 +1441,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="15">
         <v>5</v>
@@ -1456,7 +1456,7 @@
         <v>-54.545454545454</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1472,29 +1472,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="15">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="15">
+        <v>1</v>
+      </c>
+      <c r="H29" s="14">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="15">
+        <v>1</v>
+      </c>
+      <c r="K29" s="14">
+        <v>-100</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1513,29 +1513,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="15">
+        <v>1</v>
+      </c>
+      <c r="E30" s="14">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="15">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="15">
+        <v>1</v>
+      </c>
+      <c r="K30" s="14">
+        <v>-100</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1573,10 +1573,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-094pct.xlsx
+++ b/data/source/weekly/cs-en-us-094pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="15">
-        <v>4</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-50</v>
+        <v>3</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>-25</v>
+        <v>80</v>
       </c>
       <c r="I16" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J16" s="15">
         <v>25</v>
       </c>
       <c r="K16" s="14">
-        <v>-52</v>
+        <v>-40</v>
       </c>
       <c r="L16" s="14">
-        <v>-53.846153846153</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M16" s="14">
-        <v>-55.555555555555</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.638036809816</v>
+        <v>-91.573033707865</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,10 +978,10 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
         <v>0</v>
@@ -990,69 +990,69 @@
         <v>4</v>
       </c>
       <c r="G17" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>-71.428571428571</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I17" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J17" s="15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K17" s="14">
-        <v>-33.333333333333</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="L17" s="14">
-        <v>-22.580645161290</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="M17" s="14">
-        <v>71.428571428571</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N17" s="14">
-        <v>-54.716981132075</v>
+        <v>-59.016393442622</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>2</v>
       </c>
       <c r="D18" s="15">
+        <v>3</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F18" s="15">
         <v>5</v>
       </c>
-      <c r="E18" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F18" s="15">
-        <v>4</v>
-      </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>-69.230769230769</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I18" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J18" s="15">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K18" s="14">
-        <v>-46.341463414634</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L18" s="14">
-        <v>-42.105263157894</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M18" s="14">
-        <v>-54.166666666666</v>
+        <v>-52</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.971246006389</v>
+        <v>-92.727272727272</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>13</v>
+      </c>
+      <c r="D19" s="15">
         <v>11</v>
       </c>
-      <c r="D19" s="15">
-        <v>5</v>
-      </c>
       <c r="E19" s="14">
-        <v>120</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F19" s="15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G19" s="15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H19" s="14">
-        <v>12.121212121212</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I19" s="15">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="J19" s="15">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="K19" s="14">
-        <v>-11.851851851851</v>
+        <v>-10.273972602739</v>
       </c>
       <c r="L19" s="14">
-        <v>-25.157232704402</v>
+        <v>-22.485207100591</v>
       </c>
       <c r="M19" s="14">
-        <v>50.632911392405</v>
+        <v>54.117647058823</v>
       </c>
       <c r="N19" s="14">
-        <v>27.956989247311</v>
+        <v>33.673469387755</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F20" s="15">
         <v>5</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>-37.5</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I20" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J20" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K20" s="14">
-        <v>9.523809523809</v>
+        <v>13.636363636363</v>
       </c>
       <c r="L20" s="14">
-        <v>53.333333333333</v>
+        <v>47.058823529411</v>
       </c>
       <c r="M20" s="14">
-        <v>-17.857142857142</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.545454545454</v>
+        <v>-89.130434782608</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,48 +1142,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-10.526315789473</v>
+        <v>31.25</v>
       </c>
       <c r="F21" s="17">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G21" s="17">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.684210526315</v>
+        <v>-12.676056338028</v>
       </c>
       <c r="I21" s="17">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="J21" s="17">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.930232558139</v>
+        <v>-18.248175182481</v>
       </c>
       <c r="L21" s="18">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M21" s="18">
-        <v>3.553299492385</v>
+        <v>6.666666666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.829383886255</v>
+        <v>-75.083426028921</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1192,28 +1192,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I22" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J22" s="15">
         <v>10</v>
       </c>
       <c r="K22" s="14">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="L22" s="14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="15">
         <v>1</v>
       </c>
-      <c r="E23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="15">
+        <v>1</v>
       </c>
       <c r="G23" s="15">
         <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="15">
         <v>6</v>
       </c>
       <c r="K23" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L23" s="14">
         <v>-50</v>
       </c>
-      <c r="L23" s="14">
-        <v>-62.5</v>
-      </c>
       <c r="M23" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D24" s="15">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E24" s="14">
-        <v>-38.888888888888</v>
+        <v>-41.935483870967</v>
       </c>
       <c r="F24" s="15">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G24" s="15">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="H24" s="14">
-        <v>-26.086956521739</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="I24" s="15">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="J24" s="15">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="K24" s="14">
-        <v>-33.183856502242</v>
+        <v>-34.645669291338</v>
       </c>
       <c r="L24" s="14">
-        <v>-42.023346303501</v>
+        <v>-39.636363636363</v>
       </c>
       <c r="M24" s="14">
-        <v>25.210084033613</v>
+        <v>30.708661417322</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D25" s="15">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="F25" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G25" s="15">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H25" s="14">
-        <v>-42.857142857142</v>
+        <v>-43.181818181818</v>
       </c>
       <c r="I25" s="15">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="J25" s="15">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="K25" s="14">
-        <v>-55.725190839694</v>
+        <v>-54.966887417218</v>
       </c>
       <c r="L25" s="14">
-        <v>-60.810810810810</v>
+        <v>-57.232704402515</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>6</v>
+      </c>
+      <c r="D26" s="15">
         <v>8</v>
       </c>
-      <c r="D26" s="15">
-        <v>5</v>
-      </c>
       <c r="E26" s="14">
-        <v>60</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G26" s="15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I26" s="15">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J26" s="15">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="K26" s="14">
-        <v>28.333333333333</v>
+        <v>22.058823529411</v>
       </c>
       <c r="L26" s="14">
-        <v>22.222222222222</v>
+        <v>22.058823529411</v>
       </c>
       <c r="M26" s="14">
-        <v>79.069767441860</v>
+        <v>59.615384615384</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>6</v>
       </c>
       <c r="J27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="14">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="L27" s="14">
         <v>50</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>1</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K28" s="14">
-        <v>-54.545454545454</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="14">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1472,11 +1472,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="15">
-        <v>1</v>
-      </c>
-      <c r="E29" s="14">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1513,11 +1513,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="15">
-        <v>1</v>
-      </c>
-      <c r="E30" s="14">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-094pct.xlsx
+++ b/data/source/weekly/cs-en-us-094pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -923,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
         <v>300</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
         <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I16" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K16" s="14">
-        <v>-40</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L16" s="14">
-        <v>-44.444444444444</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M16" s="14">
-        <v>-46.428571428571</v>
+        <v>-48.387096774193</v>
       </c>
       <c r="N16" s="14">
-        <v>-91.573033707865</v>
+        <v>-91.397849462365</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,37 +981,37 @@
         <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F17" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H17" s="14">
-        <v>-63.636363636363</v>
+        <v>-50</v>
       </c>
       <c r="I17" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J17" s="15">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K17" s="14">
-        <v>-32.432432432432</v>
+        <v>-36.585365853658</v>
       </c>
       <c r="L17" s="14">
-        <v>-24.242424242424</v>
+        <v>-29.729729729729</v>
       </c>
       <c r="M17" s="14">
-        <v>66.666666666666</v>
+        <v>52.941176470588</v>
       </c>
       <c r="N17" s="14">
-        <v>-59.016393442622</v>
+        <v>-60.606060606060</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
         <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="15">
         <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>-64.285714285714</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="I18" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J18" s="15">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K18" s="14">
-        <v>-45.454545454545</v>
+        <v>-46.808510638297</v>
       </c>
       <c r="L18" s="14">
-        <v>-38.461538461538</v>
+        <v>-39.024390243902</v>
       </c>
       <c r="M18" s="14">
-        <v>-52</v>
+        <v>-51.923076923076</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.727272727272</v>
+        <v>-92.897727272727</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
         <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>18.181818181818</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F19" s="15">
         <v>38</v>
       </c>
       <c r="G19" s="15">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H19" s="14">
-        <v>11.764705882352</v>
+        <v>8.571428571428</v>
       </c>
       <c r="I19" s="15">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="J19" s="15">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="K19" s="14">
-        <v>-10.273972602739</v>
+        <v>-11.464968152866</v>
       </c>
       <c r="L19" s="14">
-        <v>-22.485207100591</v>
+        <v>-21.468926553672</v>
       </c>
       <c r="M19" s="14">
-        <v>54.117647058823</v>
+        <v>63.529411764705</v>
       </c>
       <c r="N19" s="14">
-        <v>33.673469387755</v>
+        <v>28.703703703703</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,38 +1103,38 @@
       <c r="C20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>-28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J20" s="15">
         <v>22</v>
       </c>
       <c r="K20" s="14">
-        <v>13.636363636363</v>
+        <v>22.727272727272</v>
       </c>
       <c r="L20" s="14">
-        <v>47.058823529411</v>
+        <v>35</v>
       </c>
       <c r="M20" s="14">
-        <v>-19.354838709677</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.130434782608</v>
+        <v>-89.243027888446</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,63 +1142,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>31.25</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="F21" s="17">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G21" s="17">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.676056338028</v>
+        <v>-13.235294117647</v>
       </c>
       <c r="I21" s="17">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="J21" s="17">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.248175182481</v>
+        <v>-19.112627986348</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.222222222222</v>
+        <v>-22.801302931596</v>
       </c>
       <c r="M21" s="18">
-        <v>6.666666666666</v>
+        <v>7.239819004524</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.083426028921</v>
+        <v>-75.440414507772</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
         <v>2</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
-        <v>3</v>
-      </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>200</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
         <v>6</v>
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="15">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="14">
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
         <v>1</v>
       </c>
       <c r="G23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="15">
         <v>4</v>
       </c>
       <c r="J23" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K23" s="14">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L23" s="14">
         <v>-50</v>
       </c>
       <c r="M23" s="14">
-        <v>-33.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E24" s="14">
-        <v>-41.935483870967</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G24" s="15">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H24" s="14">
-        <v>-38.095238095238</v>
+        <v>-40.816326530612</v>
       </c>
       <c r="I24" s="15">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="J24" s="15">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="K24" s="14">
-        <v>-34.645669291338</v>
+        <v>-35.563380281690</v>
       </c>
       <c r="L24" s="14">
-        <v>-39.636363636363</v>
+        <v>-37.328767123287</v>
       </c>
       <c r="M24" s="14">
-        <v>30.708661417322</v>
+        <v>36.567164179104</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E25" s="14">
-        <v>-55</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G25" s="15">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H25" s="14">
-        <v>-43.181818181818</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="I25" s="15">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J25" s="15">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="K25" s="14">
-        <v>-54.966887417218</v>
+        <v>-54.216867469879</v>
       </c>
       <c r="L25" s="14">
-        <v>-57.232704402515</v>
+        <v>-55.294117647058</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
         <v>25</v>
       </c>
       <c r="G26" s="15">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H26" s="14">
-        <v>-3.846153846153</v>
+        <v>31.578947368421</v>
       </c>
       <c r="I26" s="15">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J26" s="15">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K26" s="14">
-        <v>22.058823529411</v>
+        <v>22.857142857142</v>
       </c>
       <c r="L26" s="14">
-        <v>22.058823529411</v>
+        <v>14.666666666666</v>
       </c>
       <c r="M26" s="14">
-        <v>59.615384615384</v>
+        <v>40.983606557377</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,11 +1390,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>200</v>
       </c>
       <c r="L27" s="14">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
+        <v>4</v>
+      </c>
+      <c r="G28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
-      </c>
-      <c r="F28" s="15">
-        <v>1</v>
-      </c>
-      <c r="G28" s="15">
-        <v>2</v>
-      </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>300</v>
       </c>
       <c r="I28" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J28" s="15">
         <v>12</v>
       </c>
       <c r="K28" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L28" s="14">
-        <v>-14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,17 +1554,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
@@ -1573,10 +1573,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>
@@ -1622,11 +1622,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="15">
-        <v>1</v>
-      </c>
-      <c r="H33" s="14">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-094pct.xlsx
+++ b/data/source/weekly/cs-en-us-094pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -928,8 +928,8 @@
       <c r="M15" s="14">
         <v>300</v>
       </c>
-      <c r="N15" s="13" t="s">
-        <v>21</v>
+      <c r="N15" s="14">
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -946,31 +946,31 @@
         <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G16" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>60</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J16" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K16" s="14">
-        <v>-38.461538461538</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="L16" s="14">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M16" s="14">
-        <v>-48.387096774193</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="N16" s="14">
-        <v>-91.397849462365</v>
+        <v>-90.099009900990</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G17" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H17" s="14">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I17" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J17" s="15">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K17" s="14">
-        <v>-36.585365853658</v>
+        <v>-38.297872340425</v>
       </c>
       <c r="L17" s="14">
-        <v>-29.729729729729</v>
+        <v>-34.090909090909</v>
       </c>
       <c r="M17" s="14">
-        <v>52.941176470588</v>
+        <v>70.588235294117</v>
       </c>
       <c r="N17" s="14">
-        <v>-60.606060606060</v>
+        <v>-61.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
         <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" s="15">
         <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>-78.571428571428</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I18" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" s="15">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K18" s="14">
-        <v>-46.808510638297</v>
+        <v>-48</v>
       </c>
       <c r="L18" s="14">
-        <v>-39.024390243902</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="M18" s="14">
-        <v>-51.923076923076</v>
+        <v>-52.727272727272</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.897727272727</v>
+        <v>-93.066666666666</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D19" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>-27.272727272727</v>
+        <v>50</v>
       </c>
       <c r="F19" s="15">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G19" s="15">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H19" s="14">
-        <v>8.571428571428</v>
+        <v>24.324324324324</v>
       </c>
       <c r="I19" s="15">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="J19" s="15">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K19" s="14">
-        <v>-11.464968152866</v>
+        <v>-7.784431137724</v>
       </c>
       <c r="L19" s="14">
-        <v>-21.468926553672</v>
+        <v>-20.207253886010</v>
       </c>
       <c r="M19" s="14">
-        <v>63.529411764705</v>
+        <v>77.011494252873</v>
       </c>
       <c r="N19" s="14">
-        <v>28.703703703703</v>
+        <v>31.623931623931</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,38 +1103,38 @@
       <c r="C20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="15">
+        <v>4</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I20" s="15">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J20" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K20" s="14">
-        <v>22.727272727272</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L20" s="14">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="M20" s="14">
-        <v>-22.857142857142</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.243027888446</v>
+        <v>-89.090909090909</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.315789473684</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.235294117647</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="I21" s="17">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="J21" s="17">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.112627986348</v>
+        <v>-17.034700315457</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.801302931596</v>
+        <v>-22.418879056047</v>
       </c>
       <c r="M21" s="18">
-        <v>7.239819004524</v>
+        <v>12.875536480686</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.440414507772</v>
+        <v>-74.880611270296</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="15">
         <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K23" s="14">
-        <v>-42.857142857142</v>
+        <v>-37.5</v>
       </c>
       <c r="L23" s="14">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="M23" s="14">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1268,34 +1268,34 @@
         <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E24" s="14">
-        <v>-46.666666666666</v>
+        <v>-36</v>
       </c>
       <c r="F24" s="15">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G24" s="15">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H24" s="14">
-        <v>-40.816326530612</v>
+        <v>-40.384615384615</v>
       </c>
       <c r="I24" s="15">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="J24" s="15">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="K24" s="14">
-        <v>-35.563380281690</v>
+        <v>-35.275080906148</v>
       </c>
       <c r="L24" s="14">
-        <v>-37.328767123287</v>
+        <v>-34.426229508196</v>
       </c>
       <c r="M24" s="14">
-        <v>36.567164179104</v>
+        <v>38.888888888888</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
+        <v>5</v>
+      </c>
+      <c r="D25" s="15">
         <v>8</v>
       </c>
-      <c r="D25" s="15">
-        <v>15</v>
-      </c>
       <c r="E25" s="14">
-        <v>-46.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="F25" s="15">
         <v>30</v>
       </c>
       <c r="G25" s="15">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H25" s="14">
-        <v>-42.307692307692</v>
+        <v>-40</v>
       </c>
       <c r="I25" s="15">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J25" s="15">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="K25" s="14">
-        <v>-54.216867469879</v>
+        <v>-53.448275862069</v>
       </c>
       <c r="L25" s="14">
-        <v>-55.294117647058</v>
+        <v>-55</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
         <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F26" s="15">
+        <v>21</v>
+      </c>
+      <c r="G26" s="15">
+        <v>17</v>
+      </c>
+      <c r="H26" s="14">
+        <v>23.529411764705</v>
+      </c>
+      <c r="I26" s="15">
+        <v>90</v>
+      </c>
+      <c r="J26" s="15">
+        <v>72</v>
+      </c>
+      <c r="K26" s="14">
         <v>25</v>
       </c>
-      <c r="G26" s="15">
-        <v>19</v>
-      </c>
-      <c r="H26" s="14">
-        <v>31.578947368421</v>
-      </c>
-      <c r="I26" s="15">
-        <v>86</v>
-      </c>
-      <c r="J26" s="15">
-        <v>70</v>
-      </c>
-      <c r="K26" s="14">
-        <v>22.857142857142</v>
-      </c>
       <c r="L26" s="14">
-        <v>14.666666666666</v>
+        <v>13.924050632911</v>
       </c>
       <c r="M26" s="14">
-        <v>40.983606557377</v>
+        <v>45.161290322580</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="14">
-        <v>-25</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L28" s="14">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1472,17 +1472,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="15">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="14">
         <v>-100</v>
@@ -1491,7 +1491,7 @@
         <v>20</v>
       </c>
       <c r="J29" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="14">
         <v>-100</v>
@@ -1513,17 +1513,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="15">
+        <v>1</v>
+      </c>
+      <c r="E30" s="14">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="14">
         <v>-100</v>
@@ -1532,7 +1532,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="14">
         <v>-100</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-094pct.xlsx
+++ b/data/source/weekly/cs-en-us-094pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -898,29 +898,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>-100</v>
       </c>
       <c r="I15" s="15">
         <v>4</v>
       </c>
-      <c r="J15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>21</v>
+      <c r="J15" s="15">
+        <v>1</v>
+      </c>
+      <c r="K15" s="14">
+        <v>300</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
@@ -939,38 +939,38 @@
       <c r="C16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>100</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
         <v>10</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H16" s="14">
-        <v>66.666666666666</v>
+        <v>400</v>
       </c>
       <c r="I16" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J16" s="15">
         <v>27</v>
       </c>
       <c r="K16" s="14">
-        <v>-25.925925925925</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="L16" s="14">
-        <v>-28.571428571428</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M16" s="14">
-        <v>-41.176470588235</v>
+        <v>-43.589743589743</v>
       </c>
       <c r="N16" s="14">
-        <v>-90.099009900990</v>
+        <v>-89.861751152073</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,13 +978,13 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>2</v>
+      </c>
+      <c r="D17" s="15">
         <v>3</v>
       </c>
-      <c r="D17" s="15">
-        <v>6</v>
-      </c>
       <c r="E17" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="15">
         <v>8</v>
@@ -996,63 +996,63 @@
         <v>-42.857142857142</v>
       </c>
       <c r="I17" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J17" s="15">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K17" s="14">
-        <v>-38.297872340425</v>
+        <v>-36</v>
       </c>
       <c r="L17" s="14">
-        <v>-34.090909090909</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="M17" s="14">
-        <v>70.588235294117</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N17" s="14">
-        <v>-61.333333333333</v>
+        <v>-60.493827160493</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>2</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
         <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
         <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-64.285714285714</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I18" s="15">
         <v>26</v>
       </c>
       <c r="J18" s="15">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K18" s="14">
-        <v>-48</v>
+        <v>-50.943396226415</v>
       </c>
       <c r="L18" s="14">
-        <v>-43.478260869565</v>
+        <v>-46.938775510204</v>
       </c>
       <c r="M18" s="14">
-        <v>-52.727272727272</v>
+        <v>-59.375</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.066666666666</v>
+        <v>-93.450881612090</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F19" s="15">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G19" s="15">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H19" s="14">
-        <v>24.324324324324</v>
+        <v>9.302325581395</v>
       </c>
       <c r="I19" s="15">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="J19" s="15">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="K19" s="14">
-        <v>-7.784431137724</v>
+        <v>-6.741573033707</v>
       </c>
       <c r="L19" s="14">
-        <v>-20.207253886010</v>
+        <v>-18.627450980392</v>
       </c>
       <c r="M19" s="14">
-        <v>77.011494252873</v>
+        <v>72.916666666666</v>
       </c>
       <c r="N19" s="14">
-        <v>31.623931623931</v>
+        <v>34.959349593495</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F20" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>-14.285714285714</v>
+        <v>37.5</v>
       </c>
       <c r="I20" s="15">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J20" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K20" s="14">
-        <v>15.384615384615</v>
+        <v>20.689655172413</v>
       </c>
       <c r="L20" s="14">
-        <v>25</v>
+        <v>34.615384615384</v>
       </c>
       <c r="M20" s="14">
-        <v>-23.076923076923</v>
+        <v>-12.5</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.090909090909</v>
+        <v>-88.448844884488</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
         <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G21" s="17">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.564102564102</v>
+        <v>1.25</v>
       </c>
       <c r="I21" s="17">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="J21" s="17">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.034700315457</v>
+        <v>-15.680473372781</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.418879056047</v>
+        <v>-20.612813370473</v>
       </c>
       <c r="M21" s="18">
-        <v>12.875536480686</v>
+        <v>10.465116279069</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.880611270296</v>
+        <v>-74.644128113879</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,14 +1223,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
         <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
         <v>2</v>
@@ -1245,16 +1245,16 @@
         <v>5</v>
       </c>
       <c r="J23" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K23" s="14">
-        <v>-37.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L23" s="14">
-        <v>-37.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M23" s="14">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D24" s="15">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E24" s="14">
-        <v>-36</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G24" s="15">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H24" s="14">
-        <v>-40.384615384615</v>
+        <v>-35.643564356435</v>
       </c>
       <c r="I24" s="15">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="J24" s="15">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="K24" s="14">
-        <v>-35.275080906148</v>
+        <v>-34.259259259259</v>
       </c>
       <c r="L24" s="14">
-        <v>-34.426229508196</v>
+        <v>-34.055727554179</v>
       </c>
       <c r="M24" s="14">
-        <v>38.888888888888</v>
+        <v>29.090909090909</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>-37.5</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F25" s="15">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G25" s="15">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H25" s="14">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="15">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J25" s="15">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="K25" s="14">
-        <v>-53.448275862069</v>
+        <v>-53.551912568306</v>
       </c>
       <c r="L25" s="14">
-        <v>-55</v>
+        <v>-55.026455026455</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="15">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G26" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H26" s="14">
-        <v>23.529411764705</v>
+        <v>-6.25</v>
       </c>
       <c r="I26" s="15">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J26" s="15">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K26" s="14">
-        <v>25</v>
+        <v>21.052631578947</v>
       </c>
       <c r="L26" s="14">
-        <v>13.924050632911</v>
+        <v>12.195121951219</v>
       </c>
       <c r="M26" s="14">
-        <v>45.161290322580</v>
+        <v>35.294117647058</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,29 +1390,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="D27" s="15">
         <v>1</v>
       </c>
+      <c r="E27" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="15">
         <v>6</v>
       </c>
       <c r="J27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L27" s="14">
         <v>20</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="I28" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J28" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K28" s="14">
-        <v>-23.076923076923</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1472,17 +1472,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="15">
         <v>1</v>
-      </c>
-      <c r="E29" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="15">
-        <v>2</v>
       </c>
       <c r="H29" s="14">
         <v>-100</v>
@@ -1513,17 +1513,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="15">
         <v>1</v>
-      </c>
-      <c r="E30" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="15">
-        <v>2</v>
       </c>
       <c r="H30" s="14">
         <v>-100</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-094pct.xlsx
+++ b/data/source/weekly/cs-en-us-094pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -898,11 +898,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -929,7 +929,7 @@
         <v>300</v>
       </c>
       <c r="N15" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -939,38 +939,38 @@
       <c r="C16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="15">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" s="14">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="I16" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J16" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K16" s="14">
-        <v>-18.518518518518</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="L16" s="14">
-        <v>-26.666666666666</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="M16" s="14">
-        <v>-43.589743589743</v>
+        <v>-41.463414634146</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.861751152073</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G17" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>-42.857142857142</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="I17" s="15">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J17" s="15">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K17" s="14">
-        <v>-36</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L17" s="14">
-        <v>-30.434782608695</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="M17" s="14">
-        <v>77.777777777777</v>
+        <v>89.473684210526</v>
       </c>
       <c r="N17" s="14">
-        <v>-60.493827160493</v>
+        <v>-58.620689655172</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
         <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H18" s="14">
-        <v>-58.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J18" s="15">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K18" s="14">
-        <v>-50.943396226415</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="L18" s="14">
-        <v>-46.938775510204</v>
+        <v>-47.169811320754</v>
       </c>
       <c r="M18" s="14">
-        <v>-59.375</v>
+        <v>-58.208955223880</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.450881612090</v>
+        <v>-93.187347931873</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E19" s="14">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G19" s="15">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H19" s="14">
-        <v>9.302325581395</v>
+        <v>4.347826086956</v>
       </c>
       <c r="I19" s="15">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="J19" s="15">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="K19" s="14">
-        <v>-6.741573033707</v>
+        <v>-6.25</v>
       </c>
       <c r="L19" s="14">
-        <v>-18.627450980392</v>
+        <v>-17.431192660550</v>
       </c>
       <c r="M19" s="14">
-        <v>72.916666666666</v>
+        <v>73.076923076923</v>
       </c>
       <c r="N19" s="14">
-        <v>34.959349593495</v>
+        <v>38.461538461538</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>5</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="15">
         <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H20" s="14">
-        <v>37.5</v>
+        <v>-10</v>
       </c>
       <c r="I20" s="15">
         <v>35</v>
       </c>
       <c r="J20" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K20" s="14">
-        <v>20.689655172413</v>
+        <v>9.375</v>
       </c>
       <c r="L20" s="14">
-        <v>34.615384615384</v>
+        <v>25</v>
       </c>
       <c r="M20" s="14">
-        <v>-12.5</v>
+        <v>-23.913043478260</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.448844884488</v>
+        <v>-89.0625</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1145,37 +1145,37 @@
         <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="F21" s="17">
         <v>81</v>
       </c>
       <c r="G21" s="17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H21" s="18">
-        <v>1.25</v>
+        <v>-10</v>
       </c>
       <c r="I21" s="17">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="J21" s="17">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="K21" s="18">
-        <v>-15.680473372781</v>
+        <v>-15.659340659340</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.612813370473</v>
+        <v>-20.259740259740</v>
       </c>
       <c r="M21" s="18">
-        <v>10.465116279069</v>
+        <v>10.431654676259</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.644128113879</v>
+        <v>-73.983050847457</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,8 +1191,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
-        <v>2</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1226,20 +1226,20 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="15">
         <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="15">
-        <v>2</v>
       </c>
       <c r="G23" s="15">
         <v>3</v>
       </c>
       <c r="H23" s="14">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I23" s="15">
         <v>5</v>
@@ -1251,10 +1251,10 @@
         <v>-44.444444444444</v>
       </c>
       <c r="L23" s="14">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="14">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>-26.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G24" s="15">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="H24" s="14">
-        <v>-35.643564356435</v>
+        <v>-35.106382978723</v>
       </c>
       <c r="I24" s="15">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="J24" s="15">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="K24" s="14">
-        <v>-34.259259259259</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="L24" s="14">
-        <v>-34.055727554179</v>
+        <v>-33.527696793002</v>
       </c>
       <c r="M24" s="14">
-        <v>29.090909090909</v>
+        <v>32.558139534883</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25" s="15">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E25" s="14">
         <v>-55.555555555555</v>
       </c>
       <c r="F25" s="15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G25" s="15">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H25" s="14">
         <v>-50</v>
       </c>
       <c r="I25" s="15">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="J25" s="15">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="K25" s="14">
-        <v>-53.551912568306</v>
+        <v>-53.731343283582</v>
       </c>
       <c r="L25" s="14">
-        <v>-55.026455026455</v>
+        <v>-52.791878172588</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
         <v>-50</v>
       </c>
       <c r="F26" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H26" s="14">
-        <v>-6.25</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I26" s="15">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J26" s="15">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K26" s="14">
-        <v>21.052631578947</v>
+        <v>12.790697674418</v>
       </c>
       <c r="L26" s="14">
-        <v>12.195121951219</v>
+        <v>14.117647058823</v>
       </c>
       <c r="M26" s="14">
-        <v>35.294117647058</v>
+        <v>32.876712328767</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,17 +1390,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="15">
         <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="15">
-        <v>2</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D28" s="15">
         <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
         <v>9</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="I28" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K28" s="14">
-        <v>-6.666666666666</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L28" s="14">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,17 +1554,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
@@ -1573,10 +1573,10 @@
         <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>
